--- a/서버정보/20260811_리소스배포_개발.xlsx
+++ b/서버정보/20260811_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE5366C-A7C1-4759-AEA8-AE007299CDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387DA338-9E62-4C70-BEEA-4384388C6438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -2005,11 +2005,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>d-puls-ap-sbn</t>
+  </si>
+  <si>
+    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2252,7 +2252,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2366,9 +2366,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8871,7 +8868,7 @@
         <v>377</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O54" s="1" t="str">
         <f>SUBSTITUTE(F54,"hazr-","")&amp;"-osdisk"</f>
@@ -8958,7 +8955,7 @@
         <v>377</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O55" s="1" t="str">
         <f>SUBSTITUTE(F55,"hazr-","")&amp;"-osdisk"</f>
@@ -8990,7 +8987,7 @@
         <v>57</v>
       </c>
       <c r="Z55" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA55" s="1" t="b">
         <v>1</v>
@@ -9045,7 +9042,7 @@
         <v>377</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O56" s="1" t="str">
         <f>SUBSTITUTE(F56,"hazr-","")&amp;"-osdisk"</f>
@@ -9077,7 +9074,7 @@
         <v>57</v>
       </c>
       <c r="Z56" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA56" s="1" t="b">
         <v>1</v>
@@ -9132,7 +9129,7 @@
         <v>377</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O57" s="1" t="str">
         <f>SUBSTITUTE(F57,"hazr-","")&amp;"-osdisk"</f>
@@ -14801,7 +14798,7 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B72" s="38" t="s">
+      <c r="B72" s="34" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="34" t="s">
@@ -14875,7 +14872,7 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B74" s="38" t="s">
+      <c r="B74" s="34" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="34" t="s">
@@ -14929,6 +14926,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -15072,15 +15078,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
@@ -15098,6 +15095,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15113,12 +15118,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_개발.xlsx
+++ b/서버정보/20260811_리소스배포_개발.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387DA338-9E62-4C70-BEEA-4384388C6438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5976E6-0E36-4B46-B54F-8AE33D6C3FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2008,7 +2008,7 @@
     <t>d-puls-ap-sbn</t>
   </si>
   <si>
-    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
+    <t>/subscriptions/38befed7-7226-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -14920,12 +14920,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -14934,7 +14928,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -15078,23 +15072,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -15102,7 +15086,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15118,4 +15102,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>